--- a/artfynd/A 36956-2026 artfynd.xlsx
+++ b/artfynd/A 36956-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137490525</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137490523</v>
+        <v>137570580</v>
       </c>
       <c r="B3" t="n">
-        <v>96646</v>
+        <v>83407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lomtjärn, Nb</t>
+          <t>Åtibyn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>828107</v>
+        <v>828150</v>
       </c>
       <c r="R3" t="n">
-        <v>7328582</v>
+        <v>7329062</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +877,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Camilla Carlsson, Per-Anders Jonsson</t>
+          <t>Elin Kannerby, Petra Wikström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137490523</t>
+          <t>https://artportalen.se/Sighting/137570580</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137490544</v>
+        <v>137490523</v>
       </c>
       <c r="B4" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>828166</v>
+        <v>828107</v>
       </c>
       <c r="R4" t="n">
-        <v>7328559</v>
+        <v>7328582</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,16 +990,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137490544</t>
+          <t>https://artportalen.se/Sighting/137490523</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137490528</v>
+        <v>137490544</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>96650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>828078</v>
+        <v>828166</v>
       </c>
       <c r="R5" t="n">
-        <v>7328693</v>
+        <v>7328559</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,16 +1092,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137490528</t>
+          <t>https://artportalen.se/Sighting/137490544</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137490518</v>
+        <v>137570590</v>
       </c>
       <c r="B6" t="n">
-        <v>98455</v>
+        <v>92152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219815</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomtjärn, Nb</t>
+          <t>Åtibyn, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>828103</v>
+        <v>828044</v>
       </c>
       <c r="R6" t="n">
-        <v>7328588</v>
+        <v>7328710</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1163,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,65 +1193,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Camilla Carlsson, Per-Anders Jonsson</t>
+          <t>Elin Kannerby, Petra Wikström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137490518</t>
+          <t>https://artportalen.se/Sighting/137570590</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137490497</v>
+        <v>137570582</v>
       </c>
       <c r="B7" t="n">
-        <v>99712</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222812</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lomtjärn, Nb</t>
+          <t>Åtibyn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>828089</v>
+        <v>828159</v>
       </c>
       <c r="R7" t="n">
-        <v>7328622</v>
+        <v>7329045</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,27 +1305,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Camilla Carlsson, Per-Anders Jonsson</t>
+          <t>Elin Kannerby, Petra Wikström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137490497</t>
+          <t>https://artportalen.se/Sighting/137570582</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137490538</v>
+        <v>137570589</v>
       </c>
       <c r="B8" t="n">
-        <v>99712</v>
+        <v>80659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,37 +1333,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222812</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lomtjärn, Nb</t>
+          <t>Åtibyn, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>828161</v>
+        <v>828064</v>
       </c>
       <c r="R8" t="n">
-        <v>7328564</v>
+        <v>7328754</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1387,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,27 +1417,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Camilla Carlsson, Per-Anders Jonsson</t>
+          <t>Elin Kannerby, Petra Wikström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137490538</t>
+          <t>https://artportalen.se/Sighting/137570589</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137490560</v>
+        <v>137570588</v>
       </c>
       <c r="B9" t="n">
-        <v>99240</v>
+        <v>80666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,37 +1445,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223049</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lomtjärn, Nb</t>
+          <t>Åtibyn, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>828140</v>
+        <v>828064</v>
       </c>
       <c r="R9" t="n">
-        <v>7328579</v>
+        <v>7328754</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,12 +1499,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,16 +1529,3083 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Camilla Carlsson, Per-Anders Jonsson</t>
+          <t>Elin Kannerby, Petra Wikström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570588</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137490528</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lomtjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>828078</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7328693</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Camilla Carlsson, Per-Anders Jonsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137490528</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137570569</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>828141</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7328901</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570569</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137570573</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>828159</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7328942</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570573</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137570577</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>828138</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7329059</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570577</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137570581</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>828152</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7329055</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570581</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137570568</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>828142</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7328881</v>
+      </c>
+      <c r="S15" t="n">
+        <v>18</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570568</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137570572</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>828160</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7328938</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570572</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137570575</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>828153</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7329010</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570575</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137570587</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>828107</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7328825</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570587</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137570584</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58199</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>828176</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7329039</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570584</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137490518</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lomtjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>828103</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7328588</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Camilla Carlsson, Per-Anders Jonsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137490518</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137570570</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>828143</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7328903</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 10 st</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570570</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137570571</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>828159</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7328925</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ca 8 st</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570571</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137570574</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>828154</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7329008</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ca 10 st</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570574</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137570576</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>828147</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7329025</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ca 5 st</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570576</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137570579</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>828150</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7329056</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ca 10 st</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570579</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137570585</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>828178</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7328989</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570585</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137570586</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>828173</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7328901</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ca 10 st</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570586</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137570592</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>828061</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7328671</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ca 10 st</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570592</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137570593</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>828095</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7328653</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ca 20 st</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570593</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137570594</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>828095</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7328644</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ca 30 st</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570594</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137570596</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>828058</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7328643</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 10 st</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570596</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137570597</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>827990</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7328613</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 10 st</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570597</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137570599</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99440</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Åtibyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>827947</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7328626</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 20 st</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570599</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137490497</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99716</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lomtjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>828089</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7328622</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Camilla Carlsson, Per-Anders Jonsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137490497</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137490538</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99716</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lomtjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>828161</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7328564</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Camilla Carlsson, Per-Anders Jonsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137490538</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137490560</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99244</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lomtjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>828140</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7328579</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Camilla Carlsson, Per-Anders Jonsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137490560</t>
         </is>
@@ -1504,6 +4621,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
